--- a/data/UBF_room_data.xlsx
+++ b/data/UBF_room_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/scheduling/Campus-Scheduling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_F25DC773A252ABDACC104834E19C68165ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93E90484-8BD2-4D45-B2E1-8C2466F4B231}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC104834E19C68165ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4F9E65-0EC2-4EF9-8171-560CDE590C92}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,13 +87,13 @@
     <t>ILT-D10</t>
   </si>
   <si>
-    <t>Enformatik</t>
-  </si>
-  <si>
     <t>Lab</t>
   </si>
   <si>
-    <t>Enformatik 2</t>
+    <t>ENF-lab1</t>
+  </si>
+  <si>
+    <t>ENF-lab2</t>
   </si>
 </sst>
 </file>
@@ -174,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -185,7 +185,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,7 +570,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -587,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -595,7 +594,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -611,7 +610,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -619,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -627,7 +626,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -635,7 +634,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -643,7 +642,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -651,7 +650,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -659,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -667,7 +666,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -675,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -683,7 +682,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -691,7 +690,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -699,29 +698,29 @@
         <v>19</v>
       </c>
       <c r="B18" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3">
         <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3">
         <v>54</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>21</v>
+      <c r="C20" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
